--- a/stories/arbres/ATOM-REL.CON.003-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans le salon. Sa tour de cubes tombe sur le dessin de Lila. Lila a de la peine. Sami va vers elle. Il dit pardon. Il propose un geste : je t'aide à poser les cubes. Lila écoute. La peine reste un peu. Maman dit : le pardon et un geste, c'est bien. Ça n'efface pas tout de suite la peine. Sami attend. Lila hoche la tête, un peu.</t>
+          <t>Sami est dans le salon. Sa tour de cubes tombe sur le dessin de Lila. Lila a de la peine. Sami va vers elle. Il dit pardon. Il propose un geste : je t'aide à poser les cubes. Lila écoute. La peine reste un peu. Le pardon et un geste, c'est bien. Ça n'efface pas tout de suite la peine. Sami attend. Lila hoche la tête, un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est dans le salon. Sa tour de cubes tombe sur le dessin de Lila. Lila a de la peine. Sami va vers elle. Il dit pardon. Il propose un geste : je t'aide à poser les cubes. Lila écoute. La peine reste un peu.
+maman|Le pardon et un geste, c'est bien. Ça n'efface pas tout de suite la peine.
+narrateur|Sami attend. Lila hoche la tête, un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a fait une bêtise. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a dit pardon. Il a proposé un geste. La peine de Lila reste un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman pose un coussin. Sami s'assoit près de Lila.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Sami attend. Lila hoche la tête, un peu.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Sami a fait une bêtise. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Sami a dit pardon. Il a proposé un geste. La peine de Lila reste un peu.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Maman pose un coussin. Sami s'assoit près de Lila.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sami dit pardon et propose un geste</t>
+          <t>Le soleil sur la vitre embuée</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La tour d'Amir tombe sur le dessin de Nina. Il dit pardon. Il propose d'aider. Nina a encore un peu de peine. Ils attendent, puis rangent les cubes.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans le salon. Sa tour de cubes tombe sur le dessin de Lila. Lila a de la peine. Sami va vers elle. Il dit pardon. Il propose un geste : je t'aide à poser les cubes. Lila écoute. La peine reste un peu. Le pardon et un geste, c'est bien. Ça n'efface pas tout de suite la peine. Sami attend. Lila hoche la tête, un peu.</t>
+          <t>La vitre de la cuisine est toute embuée. Un petit doigt a déjà dessiné un soleil. Le soleil a huit rayons, un peu tordus. Le papier sur le tapis sent le bois. Une boîte de crayons cliquette. Maman essuie une tasse. La tasse est chaude entre ses mains. Le lait sent le miel, tout doux. Une miette reste sur la nappe à carreaux. Les carreaux sont bleus et blancs. Tu as vu le soleil sur la vitre, Amir ? Oui, maman. Il a des rayons. Nina dessine, tout près. Son papier est au sol. En ce moment, Amir pose des cubes. Sa tour grandit près du dessin. Les cubes sont verts et blancs. Ils tapent tout doux. La tour penche. Elle tombe sur le dessin de Nina. Le papier se froisse. Un trait rouge bave un peu. Nina a les yeux mouillés. Elle a de la peine. Nina a de la peine, Amir. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Je t'aide à poser les cubes. Amir ramasse un cube vert. Il le pose loin du papier. C'est un geste simple. Nina écoute. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Amir attend, les mains ouvertes. Le cube vert est loin du papier, maintenant. Nina, tu as le temps. Nina pose sa main sur le tapis. Nina hoche la tête, un peu. On laisse du temps à Nina. Tu restes près de moi ? Oui, maman. La tasse fume encore. Le soleil sur la vitre s'efface doucement. Plus tard, Nina lisse son papier. Amir pousse les cubes vers le canapé. Ils rangent tout doucement. La peine reste un peu. Bravo, Amir. C'est un beau geste. Tu as dit pardon. J'ai aidé à poser les cubes. Oui. Nina a encore un peu de peine. C'est normal. Le tapis redevient calme. Un crayon rouge attend dans la boîte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,73 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Sami est dans le salon. Sa tour de cubes tombe sur le dessin de Lila. Lila a de la peine. Sami va vers elle. Il dit pardon. Il propose un geste : je t'aide à poser les cubes. Lila écoute. La peine reste un peu.
-maman|Le pardon et un geste, c'est bien. Ça n'efface pas tout de suite la peine.
-narrateur|Sami attend. Lila hoche la tête, un peu.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vitre de la cuisine est toute embuée.
+narrateur|Un petit doigt a déjà dessiné un soleil.
+narrateur|Le soleil a huit rayons, un peu tordus.
+narrateur|Le papier sur le tapis sent le bois.
+narrateur|Une boîte de crayons cliquette.
+narrateur|Maman essuie une tasse.
+narrateur|La tasse est chaude entre ses mains.
+narrateur|Le lait sent le miel, tout doux.
+narrateur|Une miette reste sur la nappe à carreaux.
+narrateur|Les carreaux sont bleus et blancs.
+maman|Tu as vu le soleil sur la vitre, Amir ?
+enfant-m|Oui, maman.
+enfant-m|Il a des rayons.
+maman|Nina dessine, tout près.
+maman|Son papier est au sol.
+narrateur|En ce moment, Amir pose des cubes.
+narrateur|Sa tour grandit près du dessin.
+narrateur|Les cubes sont verts et blancs.
+narrateur|Ils tapent tout doux.
+narrateur|La tour penche.
+narrateur|Elle tombe sur le dessin de Nina.
+narrateur|Le papier se froisse.
+narrateur|Un trait rouge bave un peu.
+narrateur|Nina a les yeux mouillés.
+narrateur|Elle a de la peine.
+maman|Nina a de la peine, Amir.
+maman|Tu peux dire pardon.
+enfant-m|Pardon, Nina.
+maman|Tu peux proposer un geste.
+enfant-m|Je t'aide à poser les cubes.
+narrateur|Amir ramasse un cube vert.
+narrateur|Il le pose loin du papier.
+narrateur|C'est un geste simple.
+narrateur|Nina écoute.
+narrateur|Elle reste un peu triste.
+maman|La peine reste un peu.
+maman|Le pardon n'efface pas tout de suite.
+narrateur|Amir attend, les mains ouvertes.
+narrateur|Le cube vert est loin du papier, maintenant.
+maman|Nina, tu as le temps.
+narrateur|Nina pose sa main sur le tapis.
+narrateur|Nina hoche la tête, un peu.
+maman|On laisse du temps à Nina.
+maman|Tu restes près de moi ?
+enfant-m|Oui, maman.
+narrateur|La tasse fume encore.
+narrateur|Le soleil sur la vitre s'efface doucement.
+narrateur|Plus tard, Nina lisse son papier.
+narrateur|Amir pousse les cubes vers le canapé.
+narrateur|Ils rangent tout doucement.
+narrateur|La peine reste un peu.
+maman|Bravo, Amir.
+maman|C'est un beau geste.
+maman|Tu as dit pardon.
+enfant-m|J'ai aidé à poser les cubes.
+maman|Oui.
+maman|Nina a encore un peu de peine.
+maman|C'est normal.
+narrateur|Le tapis redevient calme.
+narrateur|Un crayon rouge attend dans la boîte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cubes_tombent,tasse_chaude</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1415,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sami a fait une bêtise. Que fait-il ?</t>
+          <t>Les cubes sont sur le dessin. Que fait Amir ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,7 +1571,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Sami a fait une bêtise. Que fait-il ?</t>
+          <t>narrateur|Les cubes sont sur le dessin.
+narrateur|Que fait Amir ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1526,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami a dit pardon. Il a proposé un geste. La peine de Lila reste un peu.</t>
+          <t>Amir a dit pardon. Il a proposé un geste. Il a aidé à poser les cubes. Bravo, Amir. C'est du bon travail. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,7 +1744,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sami a dit pardon. Il a proposé un geste. La peine de Lila reste un peu.</t>
+          <t>narrateur|Amir a dit pardon.
+narrateur|Il a proposé un geste.
+narrateur|Il a aidé à poser les cubes.
+maman|Bravo, Amir.
+maman|C'est du bon travail.
+maman|La peine de Nina reste un peu.
+enfant-m|J'ai dit pardon.
+maman|Oui.
+maman|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1698,7 +1780,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose un coussin. Sami s'assoit près de Lila.</t>
+          <t>Maman pose un coussin près de Nina. Amir s'assoit, tout doux. On reste ici un peu ? Oui, maman. Le papier est un peu froissé. La peine reste un peu. Je laisse du temps. Oui. Le soleil de la vitre a disparu. Il reste une petite buée. La miette est encore sur la nappe. On la ramassera ensemble, plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,7 +1916,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose un coussin. Sami s'assoit près de Lila.</t>
+          <t>narrateur|Maman pose un coussin près de Nina.
+narrateur|Amir s'assoit, tout doux.
+maman|On reste ici un peu ?
+enfant-m|Oui, maman.
+maman|Le papier est un peu froissé.
+maman|La peine reste un peu.
+enfant-m|Je laisse du temps.
+maman|Oui.
+narrateur|Le soleil de la vitre a disparu.
+narrateur|Il reste une petite buée.
+narrateur|La miette est encore sur la nappe.
+maman|On la ramassera ensemble, plus tard.
+enfant-m|D'accord, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1862,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai proposé un geste. Bravo. Tu as fait du bon travail. La tasse n'est plus chaude. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2002,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit pardon.
+enfant-m|J'ai proposé un geste.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La tasse n'est plus chaude.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2024,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-03.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami est dans le salon. Sa tour de cubes tombe sur le dessin de Lila. Lila a de la peine. Sami va vers elle. Il dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Il propose un geste : je t'aide à poser les cubes. Lila écoute. La peine reste un peu. Maman dit : le pardon et un geste, c'est bien. Ça n'efface pas tout de suite la peine. Sami attend. Lila hoche la tête, un peu.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine est toute embuée. Un petit doigt a déjà dessiné un soleil. Le soleil a huit rayons, un peu tordus. Le papier sur le tapis sent le bois. Une boîte de crayons cliquette. Maman essuie une tasse. La tasse est chaude entre ses mains. Le lait sent le miel, tout doux. Une miette reste sur la nappe à carreaux. Les carreaux sont bleus et blancs. Tu as vu le soleil sur la vitre, Amir ? Oui, maman. Il a des rayons. Nina dessine, tout près. Son papier est au sol. En ce moment, Amir pose des cubes. Sa tour grandit près du dessin. Les cubes sont verts et blancs. Ils tapent tout doux. La tour penche. Elle tombe sur le dessin de Nina. Le papier se froisse. Un trait rouge bave un peu. Nina a les yeux mouillés. Elle a de la peine. Nina a de la peine, Amir. Tu peux dire pardon. Pardon, Nina. Tu peux proposer un geste. Je t'aide à poser les cubes. Amir ramasse un cube vert. Il le pose loin du papier. C'est un geste simple. Nina écoute. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Amir attend, les mains ouvertes. Le cube vert est loin du papier, maintenant. Nina, tu as le temps. Nina pose sa main sur le tapis. Nina hoche la tête, un peu. On laisse du temps à Nina. Tu restes près de moi ? Oui, maman. La tasse fume encore. Le soleil sur la vitre s'efface doucement. Plus tard, Nina lisse son papier. Amir pousse les cubes vers le canapé. Ils rangent tout doucement. La peine reste un peu. Bravo, Amir. C'est un beau geste. Tu as dit pardon. J'ai aidé à poser les cubes. Oui. Nina a encore un peu de peine. C'est normal. Le tapis redevient calme. Un crayon rouge attend dans la boîte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Sami a fait une bêtise. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les cubes sont sur le dessin. Que fait Amir ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1575,7 +1575,6 @@
 narrateur|Que fait Amir ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1600,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir a dit pardon. Il a proposé un geste. Il a aidé à poser les cubes. Bravo, Amir. C'est du bon travail. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Amir a dit pardon. Il a proposé un geste. Il a aidé à poser les cubes. Bravo, Amir. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Sami a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Il a proposé un geste. La peine de Lila reste un peu.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a dit pardon. Il a proposé un geste. Il a aidé à poser les cubes. Bravo, Amir. La peine de Nina reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1748,14 +1747,12 @@
 narrateur|Il a proposé un geste.
 narrateur|Il a aidé à poser les cubes.
 maman|Bravo, Amir.
-maman|C'est du bon travail.
 maman|La peine de Nina reste un peu.
 enfant-m|J'ai dit pardon.
 maman|Oui.
 maman|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1785,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman pose un coussin. Sami s'assoit près de Lila.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose un coussin près de Nina. Amir s'assoit, tout doux. On reste ici un peu ? Oui, maman. Le papier est un peu froissé. La peine reste un peu. Je laisse du temps. Oui. Le soleil de la vitre a disparu. Il reste une petite buée. La miette est encore sur la nappe. On la ramassera ensemble, plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1928,6 @@
 enfant-m|D'accord, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai proposé un geste. Bravo. Tu as fait du bon travail. La tasse n'est plus chaude. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai proposé un geste. Bravo. La tasse n'est plus chaude.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai proposé un geste. Bravo. La tasse n'est plus chaude.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,12 +2095,9 @@
           <t>enfant-m|J'ai dit pardon.
 enfant-m|J'ai proposé un geste.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La tasse n'est plus chaude.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La tasse n'est plus chaude.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2161,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-03.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sami, Lila, maman</t>
+          <t>Amir, Nina, maman</t>
         </is>
       </c>
     </row>
